--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_antofagasta.xlsx
@@ -45,6 +45,12 @@
     <t xml:space="preserve">Mejillones</t>
   </si>
   <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ollagüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
@@ -54,12 +60,6 @@
     <t xml:space="preserve">Tocopilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Taltal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ollagüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:15</t>
+    <t xml:space="preserve">2026-09-10 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -550,7 +550,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2302</v>
+        <v>2104</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -563,7 +563,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -576,7 +576,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -586,10 +586,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2101</v>
+        <v>2201</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -599,10 +599,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2104</v>
+        <v>2301</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -612,10 +612,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2202</v>
+        <v>2101</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:19</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
